--- a/tumores/1. Labio y cavidad oral.xlsx
+++ b/tumores/1. Labio y cavidad oral.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A4C0C1-B379-48C1-9268-1EFF012CDFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0080EB3-6091-4849-8DCE-12D2BF0F07BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="8520" windowHeight="8880" activeTab="1" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
   <si>
     <t>T</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Carcinoma in situ</t>
   </si>
   <si>
-    <t>&gt;4 cm</t>
-  </si>
-  <si>
     <t>Subitems</t>
   </si>
   <si>
@@ -112,12 +109,6 @@
     <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
-    <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>≤3 cm y ENE+, &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -133,12 +124,6 @@
     <t>Ganglio ipsilateral &gt;3 cm ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>Ganglio/s linfáticos con ENE+ </t>
   </si>
   <si>
@@ -157,21 +142,6 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Invasión más de un subsitio</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ≤2 cm</t>
-  </si>
-  <si>
-    <t>&gt;2 cm y ≤4 cm</t>
-  </si>
-  <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -262,18 +232,12 @@
     <t>🟨 N2a: Un ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟨 N2b: Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟨 N2c: Ganglios contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
     <t>🟨 N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦 N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟦 N3b: Uno o más ganglios con ENE+</t>
   </si>
   <si>
@@ -298,10 +262,52 @@
     <t>🟥 T4a: Invasión adyacente *</t>
   </si>
   <si>
-    <t>🟥 T4b: Invasion avanzada *</t>
-  </si>
-  <si>
     <t>Inv:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ≤2 cm con DOI ≤5 mm</t>
+  </si>
+  <si>
+    <t>≤2 cm con DOI &gt;5 mm</t>
+  </si>
+  <si>
+    <t>&gt;4 cm con DOI &gt;10 mm</t>
+  </si>
+  <si>
+    <t>Entre 2 y 4 cm con DOI ≤10 mm</t>
+  </si>
+  <si>
+    <t>Entre 2 y 4 cm con DOI &gt;10 mm</t>
+  </si>
+  <si>
+    <t>&gt;4 cm con DOI ≤10 mm</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Invasión avanzada *</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm, ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm, ENE-</t>
+  </si>
+  <si>
+    <t>🟨 N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟦 N3a: Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
   </si>
 </sst>
 </file>
@@ -815,16 +821,16 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -836,7 +842,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -852,7 +858,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -868,14 +874,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -884,13 +890,15 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -898,14 +906,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -914,14 +922,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -930,14 +938,14 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -946,13 +954,15 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -960,16 +970,16 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -978,357 +988,357 @@
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="C20" s="10" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1354,13 +1364,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1368,13 +1378,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1382,13 +1392,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1396,27 +1406,27 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1424,69 +1434,69 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1494,10 +1504,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>

--- a/tumores/1. Labio y cavidad oral.xlsx
+++ b/tumores/1. Labio y cavidad oral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0080EB3-6091-4849-8DCE-12D2BF0F07BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FB203E-7013-47F2-91CE-006C953B996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>T</t>
   </si>
@@ -196,12 +196,6 @@
     <t>N3a, N3b</t>
   </si>
   <si>
-    <t xml:space="preserve"> Hueso cortical de la mandíbula, Hueso maxilar superior, Compromete el seno maxilar, Piel de la cara</t>
-  </si>
-  <si>
-    <t>Espacio masticatorio, Placas pterigoideas, Base del cráneo, Atrapamiento de arteria carótida interna</t>
-  </si>
-  <si>
     <t>TX: Tumor primario no evaluable</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>🟦 T3: &gt;4 cm con DOI ≤10 mm</t>
   </si>
   <si>
-    <t>🟥 T4: &gt;4 cm con DOI &gt;10 mm</t>
-  </si>
-  <si>
     <t>🟩 N1: Un ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
@@ -259,9 +250,6 @@
     <t>M1: Metástasis a distancia</t>
   </si>
   <si>
-    <t>🟥 T4a: Invasión adyacente *</t>
-  </si>
-  <si>
     <t>Inv:</t>
   </si>
   <si>
@@ -271,9 +259,6 @@
     <t>≤2 cm con DOI &gt;5 mm</t>
   </si>
   <si>
-    <t>&gt;4 cm con DOI &gt;10 mm</t>
-  </si>
-  <si>
     <t>Entre 2 y 4 cm con DOI ≤10 mm</t>
   </si>
   <si>
@@ -283,9 +268,6 @@
     <t>&gt;4 cm con DOI ≤10 mm</t>
   </si>
   <si>
-    <t>🟥 T4b: Invasión avanzada *</t>
-  </si>
-  <si>
     <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -308,6 +290,18 @@
   </si>
   <si>
     <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟥 T4a: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t>&gt;4 cm con DOI &gt;10 mm, Invasión de Hueso cortical de la mandíbula, Invasión de Hueso maxilar superior, Compromete el seno maxilar, Invasión de Piel de la cara</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t>Espacio masticatorio, Apófisis pterigoides, Base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -804,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93349F43-C6E5-467C-91F1-9BFB47441F05}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
@@ -842,7 +836,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -858,7 +852,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -874,14 +868,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -890,14 +884,14 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -906,14 +900,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -922,14 +916,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -938,66 +932,65 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>78</v>
+      <c r="F10" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1007,31 +1000,31 @@
       <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>71</v>
+      <c r="C12" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>72</v>
+      <c r="C13" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1041,14 +1034,14 @@
       <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>66</v>
+      <c r="C14" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1059,13 +1052,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1076,16 +1069,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
@@ -1093,16 +1086,16 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
@@ -1110,48 +1103,48 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>92</v>
+      <c r="C19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>32</v>
+      <c r="A20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1162,16 +1155,16 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>14</v>
       </c>
@@ -1179,13 +1172,13 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1196,13 +1189,16 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1213,16 +1209,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1233,13 +1226,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1250,16 +1243,16 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>14</v>
       </c>
@@ -1267,50 +1260,47 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="C28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1318,31 +1308,17 @@
         <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F32" s="2"/>
+      <c r="F31" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/tumores/1. Labio y cavidad oral.xlsx
+++ b/tumores/1. Labio y cavidad oral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FB203E-7013-47F2-91CE-006C953B996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C5E4E8-A058-464D-982C-9C9B8030BE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -295,13 +295,13 @@
     <t>🟥 T4a: Enfermedad localmente avanzada *</t>
   </si>
   <si>
-    <t>&gt;4 cm con DOI &gt;10 mm, Invasión de Hueso cortical de la mandíbula, Invasión de Hueso maxilar superior, Compromete el seno maxilar, Invasión de Piel de la cara</t>
-  </si>
-  <si>
     <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
   </si>
   <si>
-    <t>Espacio masticatorio, Apófisis pterigoides, Base del cráneo, Envuelve la carótida interna</t>
+    <t>&gt;4 cm con DOI &gt;10 mm, Invasión de hueso cortical de la mandíbula, Invasión de hueso maxilar superior, Compromete el seno maxilar, Invasión de piel de la cara</t>
+  </si>
+  <si>
+    <t>Invasión del espacio masticatorio,Invasión de apófisis pterigoides, Invasión de base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="31.77734375" style="5" customWidth="1"/>
     <col min="5" max="5" width="27.21875" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" style="5" customWidth="1"/>
     <col min="7" max="16384" width="11.5546875" style="5"/>
@@ -951,20 +951,20 @@
         <v>88</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>91</v>

--- a/tumores/1. Labio y cavidad oral.xlsx
+++ b/tumores/1. Labio y cavidad oral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C5E4E8-A058-464D-982C-9C9B8030BE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5792F253-293C-4CCA-89E7-21C010B2AE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="91">
   <si>
     <t>T</t>
   </si>
@@ -148,9 +148,6 @@
     <t>Bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Un ganglio ipsilateral &gt;3 cm , Multiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
-  </si>
-  <si>
     <t>Sin metástasis</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
     <t>M1: Metástasis a distancia</t>
   </si>
   <si>
-    <t>Inv:</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ≤2 cm con DOI ≤5 mm</t>
   </si>
   <si>
@@ -301,7 +295,10 @@
     <t>&gt;4 cm con DOI &gt;10 mm, Invasión de hueso cortical de la mandíbula, Invasión de hueso maxilar superior, Compromete el seno maxilar, Invasión de piel de la cara</t>
   </si>
   <si>
-    <t>Invasión del espacio masticatorio,Invasión de apófisis pterigoides, Invasión de base del cráneo, Envuelve la carótida interna</t>
+    <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
+  </si>
+  <si>
+    <t>Invasión del espacio masticatorio, Invasión de apófisis pterigoides, Invasión de base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -836,7 +833,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -852,7 +849,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -868,14 +865,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -884,14 +881,14 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -900,14 +897,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -916,14 +913,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -932,14 +929,14 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -948,33 +945,31 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -984,7 +979,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>17</v>
@@ -1001,7 +996,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
@@ -1018,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
@@ -1035,7 +1030,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -1052,13 +1047,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1069,13 +1064,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1086,13 +1081,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1103,13 +1098,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1120,7 +1115,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
@@ -1138,7 +1133,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>17</v>
@@ -1155,7 +1150,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>18</v>
@@ -1172,7 +1167,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -1189,7 +1184,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>27</v>
@@ -1209,13 +1204,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1226,7 +1221,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
@@ -1243,7 +1238,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>22</v>
@@ -1260,16 +1255,16 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>14</v>
       </c>
@@ -1277,10 +1272,10 @@
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>24</v>
@@ -1294,13 +1289,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1308,13 +1303,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1346,7 +1341,7 @@
         <v>33</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1360,7 +1355,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1374,7 +1369,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1388,12 +1383,12 @@
         <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
@@ -1402,7 +1397,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1410,41 +1405,41 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1452,27 +1447,27 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
